--- a/diretoria-vouchers.xlsx
+++ b/diretoria-vouchers.xlsx
@@ -472,7 +472,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Disponível</t>
+          <t>Usado</t>
         </is>
       </c>
     </row>
@@ -484,7 +484,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Disponível</t>
+          <t>Usado</t>
         </is>
       </c>
     </row>
@@ -532,7 +532,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Disponível</t>
+          <t>Usado</t>
         </is>
       </c>
     </row>
@@ -556,7 +556,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Usado</t>
+          <t>Disponível</t>
         </is>
       </c>
     </row>
